--- a/backend/data/financials_by_company/137A.T.xlsx
+++ b/backend/data/financials_by_company/137A.T.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cashflow" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="info" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="income" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cashflow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,208 +420,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO5"/>
+  <dimension ref="A1:AM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Treasury Shares Number</t>
+          <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Ordinary Shares Number</t>
+          <t>Tax Rate For Calcs</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Share Issued</t>
+          <t>Normalized EBITDA</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Net Debt</t>
+          <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Total Debt</t>
+          <t>Reconciled Depreciation</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Tangible Book Value</t>
+          <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Invested Capital</t>
+          <t>EBITDA</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Working Capital</t>
+          <t>EBIT</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Net Tangible Assets</t>
+          <t>Net Interest Income</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Common Stock Equity</t>
+          <t>Interest Expense</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Total Capitalization</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Total Equity Gross Minority Interest</t>
+          <t>Normalized Income</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Stockholders Equity</t>
+          <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Other Equity Interest</t>
+          <t>Total Expenses</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t>Total Operating Income As Reported</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Additional Paid In Capital</t>
+          <t>Diluted Average Shares</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Capital Stock</t>
+          <t>Basic Average Shares</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Common Stock</t>
+          <t>Diluted EPS</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Total Liabilities Net Minority Interest</t>
+          <t>Basic EPS</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Total Non Current Liabilities Net Minority Interest</t>
+          <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Net Income Common Stockholders</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Other Current Liabilities</t>
+          <t>Otherunder Preferred Stock Dividend</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Current Debt And Capital Lease Obligation</t>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Current Debt</t>
+          <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Payables</t>
+          <t>Net Income Continuous Operations</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Other Payable</t>
+          <t>Tax Provision</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Total Tax Payable</t>
+          <t>Pretax Income</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Total Assets</t>
+          <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Total Non Current Assets</t>
+          <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Other Non Current Assets</t>
+          <t>Total Other Finance Cost</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>Non Current Deferred Taxes Assets</t>
+          <t>Interest Expense Non Operating</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>Net PPE</t>
+          <t>Interest Income Non Operating</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Gross PPE</t>
+          <t>Operating Income</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>Machinery Furniture Equipment</t>
+          <t>Operating Expense</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Current Assets</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>Other Current Assets</t>
+          <t>Cost Of Revenue</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>Prepaid Assets</t>
+          <t>Total Revenue</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>Other Receivables</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Gross Accounts Receivable</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
     </row>
@@ -628,115 +619,113 @@
       <c r="A2" s="1" t="n">
         <v>45808</v>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
       <c r="C2" t="n">
-        <v>2971000</v>
+        <v>0.257</v>
       </c>
       <c r="D2" t="n">
-        <v>2971000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>279891000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>209170000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>274000</v>
+      </c>
       <c r="G2" t="n">
-        <v>889688000</v>
+        <v>562871000</v>
       </c>
       <c r="H2" t="n">
-        <v>889688000</v>
+        <v>279891000</v>
       </c>
       <c r="I2" t="n">
-        <v>852104000</v>
+        <v>279617000</v>
       </c>
       <c r="J2" t="n">
-        <v>889688000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>889688000</v>
-      </c>
+        <v>389000</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>889688000</v>
+        <v>389000</v>
       </c>
       <c r="M2" t="n">
-        <v>889688000</v>
+        <v>209170000</v>
       </c>
       <c r="N2" t="n">
-        <v>889688000</v>
+        <v>209170000</v>
       </c>
       <c r="O2" t="n">
-        <v>2635000</v>
+        <v>1022154000</v>
       </c>
       <c r="P2" t="n">
-        <v>428063000</v>
+        <v>279617000</v>
       </c>
       <c r="Q2" t="n">
-        <v>228995000</v>
+        <v>3257085</v>
       </c>
       <c r="R2" t="n">
-        <v>229995000</v>
+        <v>2929962</v>
       </c>
       <c r="S2" t="n">
-        <v>229995000</v>
+        <v>64.22</v>
       </c>
       <c r="T2" t="n">
-        <v>168282000</v>
+        <v>71.39</v>
       </c>
       <c r="U2" t="n">
-        <v>3000</v>
+        <v>209170000</v>
       </c>
       <c r="V2" t="n">
-        <v>168279000</v>
+        <v>209170000</v>
       </c>
       <c r="W2" t="n">
-        <v>11603000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>209170000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>209170000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>133011000</v>
+        <v>209171000</v>
       </c>
       <c r="AA2" t="n">
-        <v>41115000</v>
+        <v>72181000</v>
       </c>
       <c r="AB2" t="n">
-        <v>91896000</v>
+        <v>281352000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1057970000</v>
+        <v>1345000</v>
       </c>
       <c r="AD2" t="n">
-        <v>37586000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>636000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>36833000</v>
-      </c>
+        <v>389000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>117000</v>
+        <v>389000</v>
       </c>
       <c r="AH2" t="n">
-        <v>117000</v>
+        <v>279617000</v>
       </c>
       <c r="AI2" t="n">
-        <v>117000</v>
+        <v>459283000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1020383000</v>
+        <v>738900000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-3635000</v>
+        <v>562871000</v>
       </c>
       <c r="AL2" t="n">
-        <v>888250000</v>
+        <v>1301771000</v>
       </c>
       <c r="AM2" t="n">
-        <v>176000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>135592000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>135592000</v>
+        <v>1301771000</v>
       </c>
     </row>
     <row r="3">
@@ -747,351 +736,341 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2918600</v>
+        <v>0.262049</v>
       </c>
       <c r="D3" t="n">
-        <v>2918600</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+        <v>215444000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>149975000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>399000</v>
+      </c>
       <c r="G3" t="n">
-        <v>662774000</v>
+        <v>426779000</v>
       </c>
       <c r="H3" t="n">
-        <v>662774000</v>
+        <v>215444000</v>
       </c>
       <c r="I3" t="n">
-        <v>625406000</v>
+        <v>215045000</v>
       </c>
       <c r="J3" t="n">
-        <v>662774000</v>
+        <v>-5736000</v>
       </c>
       <c r="K3" t="n">
-        <v>662774000</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>662774000</v>
+        <v>3000</v>
       </c>
       <c r="M3" t="n">
-        <v>662774000</v>
+        <v>149975000</v>
       </c>
       <c r="N3" t="n">
-        <v>662774000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>149975000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>812701000</v>
+      </c>
       <c r="P3" t="n">
-        <v>218892000</v>
+        <v>215045000</v>
       </c>
       <c r="Q3" t="n">
-        <v>221441000</v>
+        <v>3199808</v>
       </c>
       <c r="R3" t="n">
-        <v>222441000</v>
+        <v>2807125</v>
       </c>
       <c r="S3" t="n">
-        <v>222441000</v>
+        <v>46.87</v>
       </c>
       <c r="T3" t="n">
-        <v>129420000</v>
+        <v>53.42</v>
       </c>
       <c r="U3" t="n">
-        <v>2000</v>
+        <v>149975000</v>
       </c>
       <c r="V3" t="n">
-        <v>129418000</v>
+        <v>149975000</v>
       </c>
       <c r="W3" t="n">
-        <v>3012000</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>149975000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>149975000</v>
+      </c>
       <c r="Z3" t="n">
-        <v>109598000</v>
+        <v>149976000</v>
       </c>
       <c r="AA3" t="n">
-        <v>38117000</v>
+        <v>53257000</v>
       </c>
       <c r="AB3" t="n">
-        <v>71481000</v>
+        <v>203233000</v>
       </c>
       <c r="AC3" t="n">
-        <v>792194000</v>
+        <v>-6077000</v>
       </c>
       <c r="AD3" t="n">
-        <v>37370000</v>
+        <v>-5736000</v>
       </c>
       <c r="AE3" t="n">
-        <v>7067000</v>
+        <v>5739000</v>
       </c>
       <c r="AF3" t="n">
-        <v>29912000</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>391000</v>
+        <v>3000</v>
       </c>
       <c r="AH3" t="n">
-        <v>391000</v>
+        <v>215045000</v>
       </c>
       <c r="AI3" t="n">
-        <v>391000</v>
+        <v>385922000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>754824000</v>
+        <v>600967000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2435000</v>
+        <v>426779000</v>
       </c>
       <c r="AL3" t="n">
-        <v>649561000</v>
+        <v>1027747000</v>
       </c>
       <c r="AM3" t="n">
-        <v>86000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>107612000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>107612000</v>
+        <v>1027747000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>45077</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
-        <v>2918600</v>
+        <v>0.309388</v>
       </c>
       <c r="D4" t="n">
-        <v>2918600</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>142595000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>97175000</v>
+      </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>503000</v>
       </c>
       <c r="G4" t="n">
-        <v>267158000</v>
+        <v>328173000</v>
       </c>
       <c r="H4" t="n">
-        <v>267158000</v>
+        <v>142595000</v>
       </c>
       <c r="I4" t="n">
-        <v>235515000</v>
+        <v>142092000</v>
       </c>
       <c r="J4" t="n">
-        <v>267158000</v>
+        <v>-1382000</v>
       </c>
       <c r="K4" t="n">
-        <v>267158000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>267158000</v>
-      </c>
+        <v>1382000</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>267158000</v>
+        <v>97175000</v>
       </c>
       <c r="N4" t="n">
-        <v>267158000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>97175000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>656821000</v>
+      </c>
       <c r="P4" t="n">
-        <v>68916000</v>
+        <v>140323000</v>
       </c>
       <c r="Q4" t="n">
-        <v>98621000</v>
+        <v>2730260</v>
       </c>
       <c r="R4" t="n">
-        <v>99621000</v>
+        <v>2730260</v>
       </c>
       <c r="S4" t="n">
-        <v>99621000</v>
+        <v>35.591848</v>
       </c>
       <c r="T4" t="n">
-        <v>105347000</v>
+        <v>35.591848</v>
       </c>
       <c r="U4" t="n">
-        <v>3000</v>
+        <v>97175000</v>
       </c>
       <c r="V4" t="n">
-        <v>105344000</v>
+        <v>97175000</v>
       </c>
       <c r="W4" t="n">
-        <v>2819000</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>97175000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>97175000</v>
       </c>
       <c r="Z4" t="n">
-        <v>92907000</v>
+        <v>97176000</v>
       </c>
       <c r="AA4" t="n">
-        <v>25866000</v>
+        <v>43534000</v>
       </c>
       <c r="AB4" t="n">
-        <v>67041000</v>
+        <v>140710000</v>
       </c>
       <c r="AC4" t="n">
-        <v>372505000</v>
+        <v>1769000</v>
       </c>
       <c r="AD4" t="n">
-        <v>31645000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>4008000</v>
-      </c>
+        <v>-1382000</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>27134000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>503000</v>
-      </c>
+        <v>1382000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>503000</v>
+        <v>140323000</v>
       </c>
       <c r="AI4" t="n">
-        <v>503000</v>
+        <v>328648000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>340859000</v>
+        <v>468971000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1492000</v>
+        <v>328173000</v>
       </c>
       <c r="AL4" t="n">
-        <v>257189000</v>
+        <v>797145000</v>
       </c>
       <c r="AM4" t="n">
-        <v>821000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>84341000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>84341000</v>
+        <v>797145000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>44712</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="D5" t="n">
+        <v>71711000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>48469000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>89000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>232624000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>71711000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>71622000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1119000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1119000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>48469000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>48469000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>487309000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>69829000</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2918600</v>
       </c>
-      <c r="D5" t="n">
-        <v>2918600</v>
-      </c>
-      <c r="E5" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>141060000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>181060000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>112179000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>141060000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>141060000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>141060000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>141060000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>141060000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>-28258000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>84159000</v>
-      </c>
       <c r="R5" t="n">
-        <v>85159000</v>
+        <v>465300</v>
       </c>
       <c r="S5" t="n">
-        <v>85159000</v>
+        <v>16.606935</v>
       </c>
       <c r="T5" t="n">
-        <v>99366000</v>
+        <v>104.167204</v>
       </c>
       <c r="U5" t="n">
-        <v>1000</v>
+        <v>48469000</v>
       </c>
       <c r="V5" t="n">
-        <v>99365000</v>
+        <v>48469000</v>
       </c>
       <c r="W5" t="n">
-        <v>2484000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>40000000</v>
+        <v>48469000</v>
       </c>
       <c r="Y5" t="n">
-        <v>40000000</v>
+        <v>48469000</v>
       </c>
       <c r="Z5" t="n">
-        <v>50084000</v>
+        <v>48469000</v>
       </c>
       <c r="AA5" t="n">
-        <v>19703000</v>
+        <v>22034000</v>
       </c>
       <c r="AB5" t="n">
-        <v>30381000</v>
+        <v>70503000</v>
       </c>
       <c r="AC5" t="n">
-        <v>240426000</v>
+        <v>1793000</v>
       </c>
       <c r="AD5" t="n">
-        <v>28881000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>3928000</v>
-      </c>
+        <v>-1119000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>23947000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1006000</v>
-      </c>
+        <v>1119000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>1006000</v>
+        <v>69830000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1006000</v>
+        <v>254685000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>211544000</v>
+        <v>324515000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-400000</v>
+        <v>232624000</v>
       </c>
       <c r="AL5" t="n">
-        <v>149490000</v>
+        <v>557140000</v>
       </c>
       <c r="AM5" t="n">
-        <v>166000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>62288000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>62288000</v>
+        <v>557140000</v>
       </c>
     </row>
   </sheetData>
@@ -1105,158 +1084,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AO5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Free Cash Flow</t>
+          <t>Treasury Shares Number</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Repayment Of Debt</t>
+          <t>Ordinary Shares Number</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Issuance Of Capital Stock</t>
+          <t>Share Issued</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Capital Expenditure</t>
+          <t>Net Debt</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>End Cash Position</t>
+          <t>Total Debt</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Other Cash Adjustment Outside Changein Cash</t>
+          <t>Tangible Book Value</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Beginning Cash Position</t>
+          <t>Invested Capital</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Changes In Cash</t>
+          <t>Working Capital</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Financing Cash Flow</t>
+          <t>Net Tangible Assets</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Net Other Financing Charges</t>
+          <t>Common Stock Equity</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Net Common Stock Issuance</t>
+          <t>Total Capitalization</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Common Stock Issuance</t>
+          <t>Total Equity Gross Minority Interest</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Net Issuance Payments Of Debt</t>
+          <t>Stockholders Equity</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Net Long Term Debt Issuance</t>
+          <t>Other Equity Interest</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Long Term Debt Payments</t>
+          <t>Retained Earnings</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Investing Cash Flow</t>
+          <t>Additional Paid In Capital</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Net PPE Purchase And Sale</t>
+          <t>Capital Stock</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Purchase Of PPE</t>
+          <t>Common Stock</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Total Liabilities Net Minority Interest</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Taxes Refund Paid</t>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Interest Received Cfo</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Interest Paid Cfo</t>
+          <t>Other Current Liabilities</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Current Debt And Capital Lease Obligation</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Change In Payable</t>
+          <t>Current Debt</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Change In Receivables</t>
+          <t>Payables</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
+          <t>Other Payable</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
+          <t>Total Tax Payable</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Total Assets</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Total Non Current Assets</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Net Income From Continuing Operations</t>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
         </is>
       </c>
     </row>
@@ -1264,79 +1293,115 @@
       <c r="A2" s="1" t="n">
         <v>45808</v>
       </c>
-      <c r="B2" t="n">
-        <v>221406000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>2971000</v>
+      </c>
       <c r="D2" t="n">
-        <v>15107000</v>
+        <v>2971000</v>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>878485000</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>889688000</v>
+      </c>
       <c r="H2" t="n">
-        <v>641972000</v>
+        <v>889688000</v>
       </c>
       <c r="I2" t="n">
-        <v>236513000</v>
+        <v>852104000</v>
       </c>
       <c r="J2" t="n">
-        <v>15107000</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>889688000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>889688000</v>
+      </c>
       <c r="L2" t="n">
-        <v>15107000</v>
+        <v>889688000</v>
       </c>
       <c r="M2" t="n">
-        <v>15107000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>889688000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>889688000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2635000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>428063000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>228995000</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>229995000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>229995000</v>
       </c>
       <c r="T2" t="n">
-        <v>221406000</v>
+        <v>168282000</v>
       </c>
       <c r="U2" t="n">
-        <v>-59579000</v>
+        <v>3000</v>
       </c>
       <c r="V2" t="n">
-        <v>389000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>-23782000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2997000</v>
-      </c>
+        <v>168279000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>11603000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>-27980000</v>
+        <v>133011000</v>
       </c>
       <c r="AA2" t="n">
-        <v>20115000</v>
+        <v>41115000</v>
       </c>
       <c r="AB2" t="n">
-        <v>2635000</v>
+        <v>91896000</v>
       </c>
       <c r="AC2" t="n">
-        <v>274000</v>
+        <v>1057970000</v>
       </c>
       <c r="AD2" t="n">
-        <v>274000</v>
+        <v>37586000</v>
       </c>
       <c r="AE2" t="n">
-        <v>281352000</v>
+        <v>636000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>36833000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>117000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>117000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>117000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1020383000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-3635000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>888250000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>176000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>135592000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>135592000</v>
       </c>
     </row>
     <row r="3">
@@ -1344,270 +1409,354 @@
         <v>45443</v>
       </c>
       <c r="B3" t="n">
-        <v>157217000</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2918600</v>
       </c>
       <c r="D3" t="n">
-        <v>245640000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-288000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>641972000</v>
-      </c>
+        <v>2918600</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>662774000</v>
       </c>
       <c r="H3" t="n">
-        <v>239114000</v>
+        <v>662774000</v>
       </c>
       <c r="I3" t="n">
-        <v>402857000</v>
+        <v>625406000</v>
       </c>
       <c r="J3" t="n">
-        <v>245640000</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>662774000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>662774000</v>
+      </c>
       <c r="L3" t="n">
-        <v>245640000</v>
+        <v>662774000</v>
       </c>
       <c r="M3" t="n">
-        <v>245640000</v>
+        <v>662774000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+        <v>662774000</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>218892000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-288000</v>
+        <v>221441000</v>
       </c>
       <c r="R3" t="n">
-        <v>-288000</v>
+        <v>222441000</v>
       </c>
       <c r="S3" t="n">
-        <v>-288000</v>
+        <v>222441000</v>
       </c>
       <c r="T3" t="n">
-        <v>157505000</v>
+        <v>129420000</v>
       </c>
       <c r="U3" t="n">
-        <v>-64634000</v>
+        <v>2000</v>
       </c>
       <c r="V3" t="n">
-        <v>2000</v>
+        <v>129418000</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-10078000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>12251000</v>
-      </c>
+        <v>3012000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-23270000</v>
+        <v>109598000</v>
       </c>
       <c r="AA3" t="n">
-        <v>28583000</v>
+        <v>38117000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>71481000</v>
       </c>
       <c r="AC3" t="n">
-        <v>399000</v>
+        <v>792194000</v>
       </c>
       <c r="AD3" t="n">
-        <v>399000</v>
+        <v>37370000</v>
       </c>
       <c r="AE3" t="n">
-        <v>203233000</v>
+        <v>7067000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>29912000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>391000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>391000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>391000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>754824000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-2435000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>649561000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>86000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>107612000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>107612000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>45077</v>
       </c>
-      <c r="B4" t="n">
-        <v>120306000</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>-40000000</v>
+        <v>2918600</v>
       </c>
       <c r="D4" t="n">
-        <v>28924000</v>
+        <v>2918600</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>239114000</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>267158000</v>
+      </c>
       <c r="H4" t="n">
-        <v>129883000</v>
+        <v>267158000</v>
       </c>
       <c r="I4" t="n">
-        <v>109231000</v>
+        <v>235515000</v>
       </c>
       <c r="J4" t="n">
-        <v>-11075000</v>
+        <v>267158000</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>267158000</v>
       </c>
       <c r="L4" t="n">
-        <v>28924000</v>
+        <v>267158000</v>
       </c>
       <c r="M4" t="n">
-        <v>28924000</v>
+        <v>267158000</v>
       </c>
       <c r="N4" t="n">
-        <v>-40000000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-40000000</v>
-      </c>
+        <v>267158000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-40000000</v>
+        <v>68916000</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>98621000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>99621000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>99621000</v>
       </c>
       <c r="T4" t="n">
-        <v>120306000</v>
+        <v>105347000</v>
       </c>
       <c r="U4" t="n">
-        <v>-16342000</v>
+        <v>3000</v>
       </c>
       <c r="V4" t="n">
-        <v>1000</v>
+        <v>105344000</v>
       </c>
       <c r="W4" t="n">
-        <v>-1382000</v>
+        <v>2819000</v>
       </c>
       <c r="X4" t="n">
-        <v>-14800000</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>6162000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-22052000</v>
+        <v>92907000</v>
       </c>
       <c r="AA4" t="n">
-        <v>11616000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>25866000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>67041000</v>
+      </c>
       <c r="AC4" t="n">
+        <v>372505000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>31645000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>4008000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>27134000</v>
+      </c>
+      <c r="AG4" t="n">
         <v>503000</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AH4" t="n">
         <v>503000</v>
       </c>
-      <c r="AE4" t="n">
-        <v>140710000</v>
+      <c r="AI4" t="n">
+        <v>503000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>340859000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-1492000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>257189000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>821000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>84341000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>84341000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
         <v>44712</v>
       </c>
-      <c r="B5" t="n">
-        <v>46057000</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2918600</v>
       </c>
       <c r="D5" t="n">
-        <v>10330000</v>
+        <v>2918600</v>
       </c>
       <c r="E5" t="n">
-        <v>-1095000</v>
+        <v>40000000</v>
       </c>
       <c r="F5" t="n">
-        <v>129883000</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>40000000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>141060000</v>
+      </c>
       <c r="H5" t="n">
-        <v>73496000</v>
+        <v>181060000</v>
       </c>
       <c r="I5" t="n">
-        <v>56387000</v>
+        <v>112179000</v>
       </c>
       <c r="J5" t="n">
-        <v>10330000</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>141060000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>141060000</v>
+      </c>
       <c r="L5" t="n">
-        <v>10330000</v>
+        <v>141060000</v>
       </c>
       <c r="M5" t="n">
-        <v>10330000</v>
+        <v>141060000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
+        <v>141060000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-28258000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1095000</v>
+        <v>84159000</v>
       </c>
       <c r="R5" t="n">
-        <v>-1095000</v>
+        <v>85159000</v>
       </c>
       <c r="S5" t="n">
-        <v>-1095000</v>
+        <v>85159000</v>
       </c>
       <c r="T5" t="n">
-        <v>47152000</v>
+        <v>99366000</v>
       </c>
       <c r="U5" t="n">
-        <v>-710000</v>
+        <v>1000</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>99365000</v>
       </c>
       <c r="W5" t="n">
-        <v>-1119000</v>
+        <v>2484000</v>
       </c>
       <c r="X5" t="n">
-        <v>-15366000</v>
+        <v>40000000</v>
       </c>
       <c r="Y5" t="n">
-        <v>6362000</v>
+        <v>40000000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-21889000</v>
+        <v>50084000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-6246000</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>19703000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>30381000</v>
+      </c>
       <c r="AC5" t="n">
-        <v>89000</v>
+        <v>240426000</v>
       </c>
       <c r="AD5" t="n">
-        <v>89000</v>
+        <v>28881000</v>
       </c>
       <c r="AE5" t="n">
-        <v>70503000</v>
+        <v>3928000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>23947000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1006000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1006000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1006000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>211544000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-400000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>149490000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>166000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>62288000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>62288000</v>
       </c>
     </row>
   </sheetData>
@@ -1621,6 +1770,522 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AE5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Repayment Of Debt</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Issuance Of Capital Stock</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Capital Expenditure</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>End Cash Position</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Other Cash Adjustment Outside Changein Cash</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Beginning Cash Position</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Changes In Cash</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Financing Cash Flow</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Net Other Financing Charges</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Net Common Stock Issuance</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Common Stock Issuance</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Net Issuance Payments Of Debt</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Net Long Term Debt Issuance</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Long Term Debt Payments</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Investing Cash Flow</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Net PPE Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Purchase Of PPE</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Operating Cash Flow</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Taxes Refund Paid</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Interest Received Cfo</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Interest Paid Cfo</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Change In Working Capital</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Change In Payable</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Change In Receivables</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Other Non Cash Items</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Stock Based Compensation</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Depreciation And Amortization</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing Operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B2" t="n">
+        <v>221406000</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>15107000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>878485000</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>641972000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>236513000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15107000</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>15107000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>15107000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>221406000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-59579000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>389000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>-23782000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2997000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-27980000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>20115000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2635000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>274000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>274000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>281352000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45443</v>
+      </c>
+      <c r="B3" t="n">
+        <v>157217000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>245640000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-288000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>641972000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>239114000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>402857000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>245640000</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>245640000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>245640000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-288000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-288000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-288000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>157505000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-64634000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-10078000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>12251000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-23270000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>28583000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>399000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>399000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>203233000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45077</v>
+      </c>
+      <c r="B4" t="n">
+        <v>120306000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>28924000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>239114000</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>129883000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>109231000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-11075000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>28924000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>28924000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-40000000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>120306000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-16342000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-1382000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-14800000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6162000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-22052000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>11616000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>503000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>503000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>140710000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="B5" t="n">
+        <v>46057000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10330000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1095000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>129883000</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>73496000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>56387000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10330000</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>10330000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10330000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1095000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1095000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1095000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>47152000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-710000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-1119000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-15366000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6362000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-21889000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-6246000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>89000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>89000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>70503000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:DI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2007,182 +2672,182 @@
       </c>
       <c r="BY1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="CF1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="CG1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CH1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CI1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="CJ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="CK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="CL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="CN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="CO1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
       <c r="DI1" t="inlineStr">
@@ -2279,64 +2944,64 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>560</v>
+        <v>656</v>
       </c>
       <c r="T2" t="n">
-        <v>570</v>
+        <v>656</v>
       </c>
       <c r="U2" t="n">
-        <v>560</v>
+        <v>622</v>
       </c>
       <c r="V2" t="n">
-        <v>570</v>
+        <v>658</v>
       </c>
       <c r="W2" t="n">
-        <v>560</v>
+        <v>656</v>
       </c>
       <c r="X2" t="n">
-        <v>570</v>
+        <v>656</v>
       </c>
       <c r="Y2" t="n">
-        <v>560</v>
+        <v>622</v>
       </c>
       <c r="Z2" t="n">
-        <v>570</v>
+        <v>658</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.099772</v>
+        <v>10.628962</v>
       </c>
       <c r="AC2" t="n">
-        <v>5700</v>
+        <v>25700</v>
       </c>
       <c r="AD2" t="n">
-        <v>5700</v>
+        <v>25700</v>
       </c>
       <c r="AE2" t="n">
-        <v>7010</v>
+        <v>8556</v>
       </c>
       <c r="AF2" t="n">
-        <v>11970</v>
+        <v>21840</v>
       </c>
       <c r="AG2" t="n">
-        <v>11970</v>
+        <v>21840</v>
       </c>
       <c r="AH2" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>567</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1693742336</v>
+        <v>1978049152</v>
       </c>
       <c r="AK2" t="n">
-        <v>1772380440</v>
+        <v>1947803760</v>
       </c>
       <c r="AL2" t="n">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="AM2" t="n">
         <v>1585</v>
@@ -2345,13 +3010,13 @@
         <v>4080</v>
       </c>
       <c r="AO2" t="n">
-        <v>578</v>
+        <v>549</v>
       </c>
       <c r="AP2" t="n">
-        <v>704.08</v>
+        <v>694.38</v>
       </c>
       <c r="AQ2" t="n">
-        <v>984.48</v>
+        <v>963.635</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2368,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>1253547008</v>
+        <v>1513795456</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -2389,19 +3054,19 @@
         <v>122.367</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5763974</v>
+        <v>5.3445783</v>
       </c>
       <c r="BD2" t="n">
         <v>1701302400</v>
       </c>
       <c r="BE2" t="n">
-        <v>61.54</v>
+        <v>61.53</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.55873495</v>
+        <v>-0.5041572</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.27294624</v>
+        <v>0.22635591</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -2409,7 +3074,7 @@
         </is>
       </c>
       <c r="BI2" t="n">
-        <v>560</v>
+        <v>654</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -2472,135 +3137,135 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="BY2" t="n">
+        <v>-0.30487803</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>654</v>
+      </c>
+      <c r="CA2" t="inlineStr">
         <is>
           <t>JPX</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>finmb_433389367</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>Asia/Tokyo</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>JST</t>
         </is>
       </c>
-      <c r="CD2" t="n">
+      <c r="CE2" t="n">
         <v>32400000</v>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>jp_market</t>
         </is>
       </c>
-      <c r="CF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>105</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.19125684</v>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>549.0 - 1585.0</t>
+        </is>
+      </c>
+      <c r="CK2" t="n">
+        <v>-931</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>-0.5873817</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>-50.415718</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1744369140</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1744369140</v>
+      </c>
+      <c r="CP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>-40.380005</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>-0.058152605</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>-309.635</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>-0.3213198</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>20</v>
+      </c>
+      <c r="CX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>COCOLIVE INC</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CH2" t="n">
-        <v>1780446544</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>560</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>-144.08002</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>-0.20463586</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>-424.47998</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>-0.43117177</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>20</v>
-      </c>
-      <c r="CQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>COCOLIVE INC</t>
-        </is>
-      </c>
-      <c r="CS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CT2" t="n">
+      <c r="DA2" t="n">
+        <v>1780986600</v>
+      </c>
+      <c r="DB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DC2" t="n">
         <v>1709078400000</v>
       </c>
-      <c r="CU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>560.0 - 570.0</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
+      <c r="DD2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>622.0 - 658.0</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
         <is>
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="CX2" t="n">
-        <v>7010</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>560.0 - 1585.0</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>-1025</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-0.6466877</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-55.873497</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>1744369140</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1744369140</v>
-      </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>61.54</v>
+      <c r="DG2" t="n">
+        <v>8556</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
       </c>
       <c r="DI2" t="inlineStr"/>
     </row>
